--- a/data/sars/pacific/tables/Pacific_2021_Appendix2.xlsx
+++ b/data/sars/pacific/tables/Pacific_2021_Appendix2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/pacific/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21255E2B-44B1-954F-9E64-E7ADCB3919AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B05DA51-332E-B64A-836A-349F61E8A25A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5520" yWindow="500" windowWidth="30320" windowHeight="20180" xr2:uid="{7C2DC4C9-862A-A74B-9AC3-D6637E3950D1}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="137">
   <si>
     <t>n/a</t>
   </si>
@@ -163,9 +163,6 @@
     <t>survey1</t>
   </si>
   <si>
-    <t>revised</t>
-  </si>
-  <si>
     <t>survey2</t>
   </si>
   <si>
@@ -425,13 +422,22 @@
   </si>
   <si>
     <t>survey3</t>
+  </si>
+  <si>
+    <t>revision_yr</t>
+  </si>
+  <si>
+    <t>revised_yn</t>
+  </si>
+  <si>
+    <t>yes</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -565,6 +571,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="34">
@@ -914,7 +926,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -928,6 +940,7 @@
     <xf numFmtId="3" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1303,7 +1316,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{791128B6-55A1-7448-9D4A-A7F7C8B6C5CE}">
-  <dimension ref="A1:N86"/>
+  <dimension ref="A1:O86"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="59" style="1" bestFit="1" customWidth="1"/>
@@ -1317,10 +1330,11 @@
     <col min="9" max="9" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="7.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>36</v>
       </c>
@@ -1355,18 +1369,21 @@
         <v>46</v>
       </c>
       <c r="L1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="B2" s="2">
         <v>257606</v>
@@ -1408,9 +1425,9 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B3" s="2">
         <v>30968</v>
@@ -1452,9 +1469,9 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>2</v>
@@ -1490,9 +1507,9 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>2</v>
@@ -1528,9 +1545,9 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>2</v>
@@ -1566,9 +1583,9 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>2</v>
@@ -1604,9 +1621,9 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B8" s="4">
         <v>187386</v>
@@ -1647,10 +1664,13 @@
       <c r="N8" s="3">
         <v>2021</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B9" s="2">
         <v>34187</v>
@@ -1692,9 +1712,9 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B10" s="2">
         <v>14050</v>
@@ -1736,9 +1756,9 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B11" s="4">
         <v>1437</v>
@@ -1779,10 +1799,13 @@
       <c r="N11" s="3">
         <v>2021</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B12" s="4">
         <v>4191</v>
@@ -1823,10 +1846,13 @@
       <c r="N12" s="3">
         <v>2021</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B13" s="4">
         <v>3760</v>
@@ -1867,10 +1893,13 @@
       <c r="N13" s="3">
         <v>2021</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B14" s="4">
         <v>7777</v>
@@ -1911,10 +1940,13 @@
       <c r="N14" s="3">
         <v>2021</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B15" s="4">
         <v>24685</v>
@@ -1955,10 +1987,13 @@
       <c r="N15" s="3">
         <v>2021</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B16" s="2">
         <v>21487</v>
@@ -2000,9 +2035,9 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B17" s="2">
         <v>11233</v>
@@ -2044,9 +2079,9 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B18" s="4">
         <v>16498</v>
@@ -2087,10 +2122,13 @@
       <c r="N18" s="3">
         <v>2021</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O18" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B19" s="4">
         <v>34999</v>
@@ -2131,10 +2169,13 @@
       <c r="N19" s="3">
         <v>2021</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O19" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B20" s="2">
         <v>6336</v>
@@ -2176,9 +2217,9 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B21" s="1">
         <v>453</v>
@@ -2220,9 +2261,9 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B22" s="4">
         <v>3477</v>
@@ -2263,10 +2304,13 @@
       <c r="N22" s="3">
         <v>2021</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O22" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B23" s="4">
         <v>29988</v>
@@ -2307,10 +2351,13 @@
       <c r="N23" s="3">
         <v>2021</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O23" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B24" s="4">
         <v>1056308</v>
@@ -2351,10 +2398,13 @@
       <c r="N24" s="3">
         <v>2021</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O24" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B25" s="4">
         <v>83379</v>
@@ -2395,10 +2445,13 @@
       <c r="N25" s="3">
         <v>2021</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O25" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B26" s="4">
         <v>29285</v>
@@ -2439,10 +2492,13 @@
       <c r="N26" s="3">
         <v>2021</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O26" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B27" s="1">
         <v>300</v>
@@ -2484,9 +2540,9 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B28" s="3">
         <v>72</v>
@@ -2527,10 +2583,13 @@
       <c r="N28" s="3">
         <v>2021</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O28" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B29" s="1">
         <v>836</v>
@@ -2572,9 +2631,9 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B30" s="4">
         <v>1363</v>
@@ -2615,10 +2674,13 @@
       <c r="N30" s="3">
         <v>2021</v>
       </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O30" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B31" s="2">
         <v>3044</v>
@@ -2660,9 +2722,9 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B32" s="2">
         <v>3274</v>
@@ -2704,9 +2766,9 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B33" s="2">
         <v>4111</v>
@@ -2748,9 +2810,9 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>2</v>
@@ -2792,9 +2854,9 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B35" s="2">
         <v>1997</v>
@@ -2836,9 +2898,9 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B36" s="2">
         <v>26960</v>
@@ -2880,9 +2942,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B37" s="1">
         <v>290</v>
@@ -2924,9 +2986,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B38" s="4">
         <v>4973</v>
@@ -2967,10 +3029,13 @@
       <c r="N38" s="3">
         <v>2021</v>
       </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O38" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B39" s="4">
         <v>1898</v>
@@ -3011,10 +3076,13 @@
       <c r="N39" s="3">
         <v>2021</v>
       </c>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O39" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B40" s="4">
         <v>11065</v>
@@ -3055,10 +3123,13 @@
       <c r="N40" s="3">
         <v>2021</v>
       </c>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O40" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B41" s="1">
         <v>519</v>
@@ -3100,9 +3171,9 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B42" s="3">
         <v>915</v>
@@ -3143,10 +3214,13 @@
       <c r="N42" s="3">
         <v>2021</v>
       </c>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O42" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>2</v>
@@ -3188,9 +3262,9 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B44" s="2">
         <v>76375</v>
@@ -3232,9 +3306,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>2</v>
@@ -3276,9 +3350,9 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B46" s="2">
         <v>7385</v>
@@ -3320,9 +3394,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>2</v>
@@ -3364,9 +3438,9 @@
         <v>2017</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>2</v>
@@ -3410,7 +3484,7 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>2</v>
@@ -3454,7 +3528,7 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>2</v>
@@ -3498,7 +3572,7 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>2</v>
@@ -3542,7 +3616,7 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B52" s="2">
         <v>39798</v>
@@ -3586,7 +3660,7 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>2</v>
@@ -3624,7 +3698,7 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>2</v>
@@ -3662,7 +3736,7 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>2</v>
@@ -3700,7 +3774,7 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B56" s="1">
         <v>665</v>
@@ -3744,7 +3818,7 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>0</v>
@@ -3788,7 +3862,7 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>0</v>
@@ -3832,7 +3906,7 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>2</v>
@@ -3873,7 +3947,7 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>2</v>
@@ -3914,7 +3988,7 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>2</v>
@@ -3952,7 +4026,7 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>2</v>
@@ -3990,7 +4064,7 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B63" s="2">
         <v>35179</v>
@@ -4034,7 +4108,7 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B64" s="2">
         <v>40960</v>
@@ -4076,9 +4150,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B65" s="2">
         <v>40647</v>
@@ -4120,9 +4194,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>2</v>
@@ -4164,9 +4238,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B67" s="2">
         <v>10328</v>
@@ -4208,9 +4282,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B68" s="3">
         <v>477</v>
@@ -4251,10 +4325,13 @@
       <c r="N68" s="3">
         <v>2021</v>
       </c>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O68" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B69" s="4">
         <v>2086</v>
@@ -4295,10 +4372,13 @@
       <c r="N69" s="3">
         <v>2021</v>
       </c>
-    </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O69" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B70" s="3">
         <v>167</v>
@@ -4339,10 +4419,13 @@
       <c r="N70" s="3">
         <v>2021</v>
       </c>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O70" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B71" s="2">
         <v>1329</v>
@@ -4378,9 +4461,9 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>2</v>
@@ -4422,9 +4505,9 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B73" s="1">
         <v>161</v>
@@ -4466,9 +4549,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B74" s="2">
         <v>12607</v>
@@ -4510,9 +4593,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B75" s="2">
         <v>1132</v>
@@ -4554,9 +4637,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B76" s="2">
         <v>2550</v>
@@ -4598,9 +4681,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B77" s="2">
         <v>4431</v>
@@ -4642,9 +4725,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B78" s="2">
         <v>42083</v>
@@ -4686,9 +4769,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>2</v>
@@ -4730,9 +4813,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B80" s="2">
         <v>5707</v>
@@ -4776,7 +4859,7 @@
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B81" s="1">
         <v>133</v>
@@ -4817,7 +4900,7 @@
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B82" s="1">
         <v>203</v>
@@ -4861,7 +4944,7 @@
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B83" s="1">
         <v>602</v>
@@ -4905,7 +4988,7 @@
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B84" s="1">
         <v>391</v>
@@ -4946,7 +5029,7 @@
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B85" s="1">
         <v>438</v>
@@ -4990,7 +5073,7 @@
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>2</v>
